--- a/docs/Plan_Backend_12weeks/Tracker_ke_hoach_backend_12_tuan.xlsx
+++ b/docs/Plan_Backend_12weeks/Tracker_ke_hoach_backend_12_tuan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\63200926\Downloads\Plan_Backend_12weeks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\63200926\gitHub\Backend-Order-Platform\docs\Plan_Backend_12weeks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F1F377-66F9-4E66-A781-171076AB5C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1646391C-5E51-47BA-96C8-A85B65B207D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tong_quan" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="134">
   <si>
     <t>Hạng mục</t>
   </si>
@@ -1039,6 +1039,224 @@
         <charset val="238"/>
       </rPr>
       <t xml:space="preserve">ược ở local và có dockercompose để up toàn bộ service dự án </t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ự</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ng xong Dockerfile + dockercompose app</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ự</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ng xong Dockerfile image app, docker compose, skeleton project và docs d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ự</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> án.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Thi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ế</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ế</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ki</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ế</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>n trúc d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ự</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> án architechture mà không ph</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ả</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i ki</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ế</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>n trúc trên d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ạ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ng technical.</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1887,9 +2105,13 @@
       </c>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
+    <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.45">
+      <c r="A3" s="3">
+        <v>46126</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>131</v>
+      </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2374,7 +2596,8 @@
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="3" width="26" customWidth="1"/>
+    <col min="2" max="2" width="30.58203125" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="34" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
@@ -2404,13 +2627,17 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="68" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>132</v>
+      </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>133</v>
+      </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
